--- a/data/Suspension Data Labeling Edited.xlsx
+++ b/data/Suspension Data Labeling Edited.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ФТиАД\vkr_gh\Drop_wall_impact\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{474874B1-F2A3-40E8-A428-29C572B2A843}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09DB8177-05B6-4F04-BF82-D942D5985963}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="13329" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1163,7 +1163,7 @@
         <v>21</v>
       </c>
       <c r="C23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="s">
         <v>19</v>
@@ -1195,7 +1195,7 @@
         <v>22</v>
       </c>
       <c r="C24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
         <v>19</v>
@@ -1550,7 +1550,7 @@
         <v>33</v>
       </c>
       <c r="C35">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D35" t="s">
         <v>19</v>
@@ -1678,7 +1678,7 @@
         <v>37</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D39" t="s">
         <v>19</v>
@@ -1742,7 +1742,7 @@
         <v>39</v>
       </c>
       <c r="C41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D41" t="s">
         <v>19</v>
@@ -2161,7 +2161,7 @@
         <v>52</v>
       </c>
       <c r="C54">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D54">
         <v>0</v>
@@ -2225,7 +2225,7 @@
         <v>54</v>
       </c>
       <c r="C56">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D56">
         <v>0</v>
@@ -2449,7 +2449,7 @@
         <v>61</v>
       </c>
       <c r="C63">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D63">
         <v>0</v>
@@ -2513,7 +2513,7 @@
         <v>63</v>
       </c>
       <c r="C65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D65">
         <v>0</v>
@@ -2545,7 +2545,7 @@
         <v>64</v>
       </c>
       <c r="C66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D66">
         <v>0</v>
@@ -2577,7 +2577,7 @@
         <v>65</v>
       </c>
       <c r="C67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D67">
         <v>0</v>
@@ -2609,7 +2609,7 @@
         <v>66</v>
       </c>
       <c r="C68">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D68">
         <v>0</v>
@@ -3092,7 +3092,7 @@
         <v>81</v>
       </c>
       <c r="C83">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D83">
         <v>5</v>
@@ -3124,7 +3124,7 @@
         <v>82</v>
       </c>
       <c r="C84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D84" t="s">
         <v>19</v>
@@ -3188,7 +3188,7 @@
         <v>84</v>
       </c>
       <c r="C86">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D86" t="s">
         <v>19</v>
@@ -3284,7 +3284,7 @@
         <v>87</v>
       </c>
       <c r="C89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D89" t="s">
         <v>19</v>
@@ -3316,7 +3316,7 @@
         <v>88</v>
       </c>
       <c r="C90">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D90" t="s">
         <v>19</v>
@@ -3348,7 +3348,7 @@
         <v>89</v>
       </c>
       <c r="C91">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D91" t="s">
         <v>19</v>
@@ -3444,7 +3444,7 @@
         <v>92</v>
       </c>
       <c r="C94">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D94" t="s">
         <v>19</v>
@@ -4308,7 +4308,7 @@
         <v>119</v>
       </c>
       <c r="C121">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D121">
         <v>3</v>
@@ -4340,7 +4340,7 @@
         <v>120</v>
       </c>
       <c r="C122">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D122">
         <v>0</v>
@@ -4436,7 +4436,7 @@
         <v>123</v>
       </c>
       <c r="C125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D125" t="s">
         <v>19</v>
@@ -5140,7 +5140,7 @@
         <v>145</v>
       </c>
       <c r="C147">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D147">
         <v>1</v>
@@ -5364,7 +5364,7 @@
         <v>152</v>
       </c>
       <c r="C154">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D154" t="s">
         <v>19</v>
@@ -5396,7 +5396,7 @@
         <v>153</v>
       </c>
       <c r="C155">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D155" t="s">
         <v>19</v>
@@ -5556,7 +5556,7 @@
         <v>158</v>
       </c>
       <c r="C160">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D160" t="s">
         <v>19</v>
@@ -5620,7 +5620,7 @@
         <v>160</v>
       </c>
       <c r="C162">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D162" t="s">
         <v>19</v>
@@ -5684,7 +5684,7 @@
         <v>162</v>
       </c>
       <c r="C164">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D164" t="s">
         <v>19</v>
@@ -6292,7 +6292,7 @@
         <v>181</v>
       </c>
       <c r="C183">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D183" t="s">
         <v>19</v>
@@ -6324,7 +6324,7 @@
         <v>182</v>
       </c>
       <c r="C184">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D184">
         <v>0</v>
@@ -6516,7 +6516,7 @@
         <v>188</v>
       </c>
       <c r="C190">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D190" t="s">
         <v>19</v>
@@ -7028,7 +7028,7 @@
         <v>204</v>
       </c>
       <c r="C206">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D206" t="s">
         <v>19</v>
@@ -7220,7 +7220,7 @@
         <v>210</v>
       </c>
       <c r="C212">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D212" t="s">
         <v>19</v>
@@ -7572,7 +7572,7 @@
         <v>221</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D223" t="s">
         <v>19</v>
@@ -7764,7 +7764,7 @@
         <v>227</v>
       </c>
       <c r="C229">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D229" t="s">
         <v>19</v>
@@ -7924,7 +7924,7 @@
         <v>232</v>
       </c>
       <c r="C234">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D234">
         <v>0</v>
@@ -8244,7 +8244,7 @@
         <v>242</v>
       </c>
       <c r="C244">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D244">
         <v>0</v>
@@ -8404,7 +8404,7 @@
         <v>247</v>
       </c>
       <c r="C249">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D249">
         <v>0</v>
@@ -8692,7 +8692,7 @@
         <v>256</v>
       </c>
       <c r="C258">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D258">
         <v>0</v>
@@ -8820,7 +8820,7 @@
         <v>260</v>
       </c>
       <c r="C262">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D262">
         <v>0</v>
@@ -9076,7 +9076,7 @@
         <v>268</v>
       </c>
       <c r="C270">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D270" t="s">
         <v>19</v>
@@ -9332,7 +9332,7 @@
         <v>276</v>
       </c>
       <c r="C278">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D278">
         <v>0</v>
@@ -9495,7 +9495,7 @@
         <v>281</v>
       </c>
       <c r="C283">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D283">
         <v>2</v>
@@ -9687,7 +9687,7 @@
         <v>287</v>
       </c>
       <c r="C289">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D289">
         <v>2</v>
@@ -10679,7 +10679,7 @@
         <v>318</v>
       </c>
       <c r="C320">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D320" t="s">
         <v>19</v>
@@ -11319,7 +11319,7 @@
         <v>338</v>
       </c>
       <c r="C340">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D340">
         <v>0</v>
@@ -12311,7 +12311,7 @@
         <v>369</v>
       </c>
       <c r="C371">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D371" t="s">
         <v>19</v>
@@ -12663,7 +12663,7 @@
         <v>380</v>
       </c>
       <c r="C382">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D382">
         <v>0</v>
@@ -12887,7 +12887,7 @@
         <v>387</v>
       </c>
       <c r="C389">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D389">
         <v>0</v>
